--- a/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/Cancer_Magadan_2021-2023.xlsx
+++ b/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/Cancer_Magadan_2021-2023.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9144" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9324" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="SEA OF OKHOTSK" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Magadan_cancer_prevalence!$B$1:$E$58</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2142,7 +2155,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="6">
     <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
@@ -10951,7 +10964,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -11857,7 +11870,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:E58">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:E58" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="E1">
